--- a/diseases/d127/2020-2025.xlsx
+++ b/diseases/d127/2020-2025.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -3083,9 +3080,6 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">

--- a/diseases/d127/2020-2025.xlsx
+++ b/diseases/d127/2020-2025.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -776,68 +773,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -864,17 +875,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -913,17 +924,34 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -931,6 +959,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -948,7 +1034,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -961,42 +1047,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1023,17 +1109,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1072,165 +1158,79 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>1</v>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2020-02</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1306,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1317,68 +1314,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1405,17 +1416,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1440,12 +1451,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1454,79 +1465,165 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1685,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2020-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1736,12 +1833,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2020-05</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1884,12 +1981,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2032,12 +2129,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-05</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2180,12 +2277,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2328,12 +2425,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2476,12 +2573,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2020-10</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2624,12 +2721,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2772,12 +2869,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2020-10</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2920,12 +3017,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3038,12 +3135,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3068,12 +3165,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3082,6 +3179,9 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3090,82 +3190,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3192,17 +3278,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3241,34 +3327,17 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3276,64 +3345,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN18" t="b">
-        <v>1</v>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3351,7 +3362,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -3364,42 +3375,42 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3426,17 +3437,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3461,12 +3472,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3475,79 +3486,165 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3706,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3727,12 +3824,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3757,12 +3854,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3771,9 +3868,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3782,68 +3876,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3870,17 +3978,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3905,12 +4013,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3919,79 +4027,165 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4247,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4201,12 +4395,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4349,12 +4543,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4497,12 +4691,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4645,12 +4839,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4793,12 +4987,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4941,12 +5135,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5089,12 +5283,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5237,12 +5431,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5385,12 +5579,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5533,12 +5727,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5651,12 +5845,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5681,12 +5875,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5695,9 +5889,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -5706,68 +5897,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5794,17 +5999,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5829,12 +6034,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5843,79 +6048,165 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5977,12 +6268,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6125,12 +6416,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6273,12 +6564,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6421,12 +6712,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6569,12 +6860,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6717,12 +7008,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6865,12 +7156,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7013,12 +7304,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7161,12 +7452,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7309,12 +7600,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7457,12 +7748,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7605,12 +7896,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7723,12 +8014,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7753,12 +8044,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7767,9 +8058,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -7778,68 +8066,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7866,17 +8168,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7901,12 +8203,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7915,79 +8217,165 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN49" t="b">
+        <v>1</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8049,12 +8437,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8197,12 +8585,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8345,12 +8733,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8493,12 +8881,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8641,12 +9029,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8789,12 +9177,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8937,12 +9325,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -9085,12 +9473,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9233,12 +9621,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9381,12 +9769,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9529,12 +9917,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9677,12 +10065,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9825,12 +10213,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9973,12 +10361,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10121,12 +10509,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -10269,12 +10657,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10417,12 +10805,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10565,12 +10953,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -10713,12 +11101,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -10861,12 +11249,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -11009,12 +11397,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11157,12 +11545,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11305,12 +11693,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -11453,12 +11841,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11601,12 +11989,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11749,12 +12137,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11897,12 +12285,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -12045,12 +12433,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12130,6 +12518,1190 @@
         </is>
       </c>
       <c r="BC77" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -12251,7 +13823,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -12261,7 +13833,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -12281,7 +13853,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -12291,7 +13863,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
